--- a/artfynd/A 53801-2024 artfynd.xlsx
+++ b/artfynd/A 53801-2024 artfynd.xlsx
@@ -769,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 53801-2024 artfynd.xlsx
+++ b/artfynd/A 53801-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122595962</v>
       </c>
       <c r="B2" t="n">
-        <v>97191</v>
+        <v>97194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53801-2024 artfynd.xlsx
+++ b/artfynd/A 53801-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122595962</v>
       </c>
       <c r="B2" t="n">
-        <v>97301</v>
+        <v>97309</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53801-2024 artfynd.xlsx
+++ b/artfynd/A 53801-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122595962</v>
       </c>
       <c r="B2" t="n">
-        <v>97309</v>
+        <v>97311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53801-2024 artfynd.xlsx
+++ b/artfynd/A 53801-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122595962</v>
       </c>
       <c r="B2" t="n">
-        <v>97311</v>
+        <v>97319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
